--- a/tabtools/qa/baseline/workbooks/crosstab_3x3_chi2.xlsx
+++ b/tabtools/qa/baseline/workbooks/crosstab_3x3_chi2.xlsx
@@ -97,7 +97,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="208">
+  <fonts count="236">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -803,6 +803,118 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -969,7 +1081,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="154">
+  <borders count="182">
     <border>
       <left/>
       <right/>
@@ -1891,6 +2003,202 @@
       <left style="none"/>
       <right style="none"/>
       <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -2004,7 +2312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -2586,14 +2894,126 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" xfId="0"/>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2606,14 +3026,14 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="146" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="147" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" style="148" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" style="149" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" style="150" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" style="151" customWidth="true"/>
-    <col min="7" max="7" width="14.7109375" style="152" customWidth="true"/>
-    <col min="8" max="8" width="14.7109375" style="153" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="174" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="175" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" style="176" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="177" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" style="178" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" style="179" customWidth="true"/>
+    <col min="7" max="7" width="14.7109375" style="180" customWidth="true"/>
+    <col min="8" max="8" width="14.7109375" style="181" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2750,31 +3170,32 @@
       <c r="A6" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="167" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="126" t="s">
+      <c r="C6" s="168" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="127" t="s">
+      <c r="D6" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="128" t="s">
+      <c r="E6" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="129" t="s">
+      <c r="F6" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="130" t="s">
+      <c r="G6" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="131" t="s">
+      <c r="H6" s="173" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B6:H6"/>
   </mergeCells>
 </worksheet>
 </file>